--- a/sources/table_normalization/xlsx/employment-table25.xlsx
+++ b/sources/table_normalization/xlsx/employment-table25.xlsx
@@ -161,11 +161,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -478,7 +482,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
@@ -493,8 +497,8 @@
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -503,21 +507,21 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -525,15 +529,15 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="38" customHeight="1">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -544,8 +548,8 @@
         <v>10</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
